--- a/Budget.xlsx
+++ b/Budget.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\BING Elektries en Elektronies\Jaar 3\Semester 2\EEII 327 Electrical Design\Components\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3dddac90b051cdc0/Documents/Y3_s2/MCTR327/Git_Repo/Design-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6C40F99-BF42-4013-8662-E13F410A9EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{F6C40F99-BF42-4013-8662-E13F410A9EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E79B7AA-320D-485E-8133-FAD93058B134}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{F95D818F-1442-4D5C-BB71-671235377480}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{F95D818F-1442-4D5C-BB71-671235377480}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
   <si>
     <t>Part</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>Connector 3</t>
+  </si>
+  <si>
+    <t>Motor driver</t>
+  </si>
+  <si>
+    <t>DC Motor</t>
   </si>
 </sst>
 </file>
@@ -639,24 +645,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233B493-35C4-4F44-9A6D-F7C131D637A7}">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.89453125" customWidth="1"/>
+    <col min="4" max="4" width="16.5234375" customWidth="1"/>
+    <col min="7" max="7" width="19.41796875" customWidth="1"/>
+    <col min="8" max="8" width="15.1015625" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="8.33203125" customWidth="1"/>
+    <col min="12" max="12" width="8.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -670,7 +676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -685,7 +691,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
@@ -700,7 +706,7 @@
         <v>349.6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
@@ -715,7 +721,7 @@
         <v>248.4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="7" t="s">
         <v>15</v>
       </c>
@@ -730,7 +736,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -745,7 +751,7 @@
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A9" s="7" t="s">
         <v>17</v>
       </c>
@@ -760,7 +766,7 @@
         <v>314.48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
@@ -781,7 +787,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A11" s="7" t="s">
         <v>19</v>
       </c>
@@ -799,11 +805,11 @@
         <v>11</v>
       </c>
       <c r="H11" s="16">
-        <f>H10-(D15+D28+D42+D56+D70)</f>
-        <v>3850.5149999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <f>H10-SUM(D4:D70)</f>
+        <v>1144.8699999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
@@ -812,7 +818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
@@ -821,7 +827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A14" s="7" t="s">
         <v>4</v>
       </c>
@@ -836,7 +842,7 @@
         <v>135.69999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A15" s="12" t="s">
         <v>3</v>
       </c>
@@ -847,17 +853,17 @@
         <v>1149.4850000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="3"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="3"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -865,12 +871,12 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B19" s="3"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4" t="s">
         <v>0</v>
       </c>
@@ -884,7 +890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="7"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9"/>
@@ -893,7 +899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="7"/>
       <c r="B22" s="8"/>
       <c r="C22" s="9"/>
@@ -902,7 +908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="7"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9"/>
@@ -911,7 +917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="7"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
@@ -920,7 +926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="7"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
@@ -929,7 +935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="7"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
@@ -938,7 +944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A27" s="7" t="s">
         <v>4</v>
       </c>
@@ -949,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A28" s="12" t="s">
         <v>3</v>
       </c>
@@ -960,22 +966,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="3"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="3"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="3"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2" t="s">
         <v>7</v>
       </c>
@@ -983,12 +989,12 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B33" s="3"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4" t="s">
         <v>0</v>
       </c>
@@ -1002,25 +1008,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="7"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="9"/>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="8">
+        <v>2</v>
+      </c>
+      <c r="C35" s="9">
+        <v>126.85</v>
+      </c>
       <c r="D35" s="10">
         <f>B35*C35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="7"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
+        <v>253.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="8">
+        <v>2</v>
+      </c>
+      <c r="C36" s="9">
+        <v>204.69</v>
+      </c>
       <c r="D36" s="10">
         <f t="shared" ref="D36:D41" si="2">B36*C36</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+        <v>409.38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="7"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
@@ -1029,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="7"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
@@ -1038,7 +1056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="7"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
@@ -1047,7 +1065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="7"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
@@ -1056,18 +1074,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A41" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="9"/>
+      <c r="B41" s="8">
+        <v>1</v>
+      </c>
+      <c r="C41" s="9">
+        <v>115</v>
+      </c>
       <c r="D41" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A42" s="12" t="s">
         <v>3</v>
       </c>
@@ -1075,25 +1097,25 @@
       <c r="C42" s="14"/>
       <c r="D42" s="15">
         <f>SUM(D35:D41)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+        <v>778.07999999999993</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="3"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="3"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="3"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2" t="s">
         <v>8</v>
       </c>
@@ -1101,12 +1123,12 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B47" s="3"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
@@ -1120,7 +1142,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="7"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
@@ -1129,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="7"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
@@ -1138,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="7"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
@@ -1147,7 +1169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="7"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
@@ -1156,7 +1178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="7"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
@@ -1165,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="7"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
@@ -1174,7 +1196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A55" s="7" t="s">
         <v>4</v>
       </c>
@@ -1185,7 +1207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A56" s="12" t="s">
         <v>3</v>
       </c>
@@ -1196,22 +1218,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="3"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="3"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="3"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="2" t="s">
         <v>9</v>
       </c>
@@ -1219,12 +1241,12 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
     </row>
-    <row r="61" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B61" s="3"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="4" t="s">
         <v>0</v>
       </c>
@@ -1238,7 +1260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="7"/>
       <c r="B63" s="8"/>
       <c r="C63" s="9"/>
@@ -1247,7 +1269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="7"/>
       <c r="B64" s="8"/>
       <c r="C64" s="9"/>
@@ -1256,7 +1278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="7"/>
       <c r="B65" s="8"/>
       <c r="C65" s="9"/>
@@ -1265,7 +1287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="7"/>
       <c r="B66" s="8"/>
       <c r="C66" s="9"/>
@@ -1274,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="7"/>
       <c r="B67" s="8"/>
       <c r="C67" s="9"/>
@@ -1283,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="7"/>
       <c r="B68" s="8"/>
       <c r="C68" s="9"/>
@@ -1292,7 +1314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A69" s="7" t="s">
         <v>4</v>
       </c>
@@ -1303,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A70" s="12" t="s">
         <v>3</v>
       </c>

--- a/Budget.xlsx
+++ b/Budget.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3dddac90b051cdc0/Documents/Y3_s2/MCTR327/Git_Repo/Design-2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\GitHub\Design-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{F6C40F99-BF42-4013-8662-E13F410A9EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E79B7AA-320D-485E-8133-FAD93058B134}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15453FC3-0638-466C-8015-A28EF794BB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{F95D818F-1442-4D5C-BB71-671235377480}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95D818F-1442-4D5C-BB71-671235377480}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -645,24 +645,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233B493-35C4-4F44-9A6D-F7C131D637A7}">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="3" max="3" width="13.89453125" customWidth="1"/>
-    <col min="4" max="4" width="16.5234375" customWidth="1"/>
-    <col min="7" max="7" width="19.41796875" customWidth="1"/>
-    <col min="8" max="8" width="15.1015625" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="7" max="7" width="19.453125" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="8.3125" customWidth="1"/>
+    <col min="12" max="12" width="8.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -676,7 +676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -691,7 +691,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
@@ -706,7 +706,7 @@
         <v>349.6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
@@ -721,7 +721,7 @@
         <v>248.4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>15</v>
       </c>
@@ -736,7 +736,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -751,7 +751,7 @@
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="7" t="s">
         <v>17</v>
       </c>
@@ -766,7 +766,7 @@
         <v>314.48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
@@ -787,7 +787,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
         <v>19</v>
       </c>
@@ -805,11 +805,11 @@
         <v>11</v>
       </c>
       <c r="H11" s="16">
-        <f>H10-SUM(D4:D70)</f>
-        <v>1144.8699999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <f>H10-(D15+D28+D42+D56+D70)</f>
+        <v>3072.4349999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
         <v>4</v>
       </c>
@@ -842,7 +842,7 @@
         <v>135.69999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="12" t="s">
         <v>3</v>
       </c>
@@ -853,17 +853,17 @@
         <v>1149.4850000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B16" s="3"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -871,12 +871,12 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="3"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>0</v>
       </c>
@@ -890,7 +890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9"/>
@@ -899,7 +899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="7"/>
       <c r="B22" s="8"/>
       <c r="C22" s="9"/>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="7"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9"/>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="7"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="7"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="7"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
         <v>4</v>
       </c>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="12" t="s">
         <v>3</v>
       </c>
@@ -966,22 +966,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B29" s="3"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B30" s="3"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B31" s="3"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>7</v>
       </c>
@@ -989,12 +989,12 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B33" s="3"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>20</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>253.7</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>21</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>409.38</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="7"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="7"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="7"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="7"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="7" t="s">
         <v>4</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="12" t="s">
         <v>3</v>
       </c>
@@ -1100,22 +1100,22 @@
         <v>778.07999999999993</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B43" s="3"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B44" s="3"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B45" s="3"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>8</v>
       </c>
@@ -1123,12 +1123,12 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="3"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="7"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="7"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
@@ -1160,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="7"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="7"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="7"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="7"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
@@ -1196,7 +1196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="7" t="s">
         <v>4</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="12" t="s">
         <v>3</v>
       </c>
@@ -1218,22 +1218,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B57" s="3"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B58" s="3"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B59" s="3"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>9</v>
       </c>
@@ -1241,12 +1241,12 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
     </row>
-    <row r="61" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="3"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>0</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="7"/>
       <c r="B63" s="8"/>
       <c r="C63" s="9"/>
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="7"/>
       <c r="B64" s="8"/>
       <c r="C64" s="9"/>
@@ -1278,7 +1278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="7"/>
       <c r="B65" s="8"/>
       <c r="C65" s="9"/>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="7"/>
       <c r="B66" s="8"/>
       <c r="C66" s="9"/>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="7"/>
       <c r="B67" s="8"/>
       <c r="C67" s="9"/>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="7"/>
       <c r="B68" s="8"/>
       <c r="C68" s="9"/>
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="7" t="s">
         <v>4</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="12" t="s">
         <v>3</v>
       </c>

--- a/Budget.xlsx
+++ b/Budget.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\Documents\GitHub\Design-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viank\Documents\NWU Meg B.Eng\3rde jaar\MCTR 327_Engineering Design\Git_repository\Design-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15453FC3-0638-466C-8015-A28EF794BB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C5EDE9-8375-48D6-B093-9C72024FDCC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F95D818F-1442-4D5C-BB71-671235377480}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F95D818F-1442-4D5C-BB71-671235377480}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
   <si>
     <t>Part</t>
   </si>
@@ -105,6 +105,15 @@
   </si>
   <si>
     <t>DC Motor</t>
+  </si>
+  <si>
+    <t>HX711 LOAD CELL AMPLIFIER</t>
+  </si>
+  <si>
+    <t>Privately orderd</t>
+  </si>
+  <si>
+    <t>YZC LOAD CELL - 100KG - S SHAPE</t>
   </si>
 </sst>
 </file>
@@ -114,7 +123,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R&quot;* #,##0.00_-;\-&quot;R&quot;* #,##0.00_-;_-&quot;R&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +134,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -281,7 +298,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -309,6 +326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -645,24 +663,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2233B493-35C4-4F44-9A6D-F7C131D637A7}">
   <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="3" max="3" width="13.90625" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="7" max="7" width="19.453125" customWidth="1"/>
-    <col min="8" max="8" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.44140625" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="8.26953125" customWidth="1"/>
+    <col min="12" max="12" width="8.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -676,7 +695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
@@ -691,7 +710,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
@@ -706,7 +725,7 @@
         <v>349.6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
@@ -721,7 +740,7 @@
         <v>248.4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>15</v>
       </c>
@@ -736,7 +755,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
@@ -751,7 +770,7 @@
         <v>12.074999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>17</v>
       </c>
@@ -766,7 +785,7 @@
         <v>314.48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
@@ -787,7 +806,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>19</v>
       </c>
@@ -806,10 +825,10 @@
       </c>
       <c r="H11" s="16">
         <f>H10-(D15+D28+D42+D56+D70)</f>
-        <v>3072.4349999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>2535.3849999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
@@ -818,7 +837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
@@ -827,7 +846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>4</v>
       </c>
@@ -842,7 +861,7 @@
         <v>135.69999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>3</v>
       </c>
@@ -853,17 +872,17 @@
         <v>1149.4850000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -871,12 +890,12 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="3"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>0</v>
       </c>
@@ -890,7 +909,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9"/>
@@ -899,7 +918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="8"/>
       <c r="C22" s="9"/>
@@ -908,7 +927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9"/>
@@ -917,7 +936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
@@ -926,7 +945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
@@ -935,7 +954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
@@ -944,7 +963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>4</v>
       </c>
@@ -955,7 +974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>3</v>
       </c>
@@ -966,22 +985,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B29" s="3"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>7</v>
       </c>
@@ -989,12 +1008,12 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="3"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +1027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>20</v>
       </c>
@@ -1023,7 +1042,7 @@
         <v>253.7</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>21</v>
       </c>
@@ -1038,7 +1057,7 @@
         <v>409.38</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
@@ -1047,7 +1066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
@@ -1056,7 +1075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
@@ -1065,7 +1084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
@@ -1074,7 +1093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>4</v>
       </c>
@@ -1089,7 +1108,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
         <v>3</v>
       </c>
@@ -1100,22 +1119,22 @@
         <v>778.07999999999993</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B43" s="3"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B44" s="3"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B45" s="3"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>8</v>
       </c>
@@ -1123,12 +1142,12 @@
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="3"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
@@ -1142,25 +1161,43 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="7"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="9"/>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="8">
+        <v>1</v>
+      </c>
+      <c r="C49" s="9">
+        <v>493.35</v>
+      </c>
       <c r="D49" s="10">
         <f>B49*C49</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="7"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="9"/>
+        <v>493.35</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="8">
+        <v>1</v>
+      </c>
+      <c r="C50" s="9">
+        <v>43.7</v>
+      </c>
       <c r="D50" s="10">
         <f t="shared" ref="D50:D55" si="3">B50*C50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+        <v>43.7</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="7"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
@@ -1169,7 +1206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="7"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
@@ -1178,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="7"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
@@ -1187,7 +1224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="7"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
@@ -1196,7 +1233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>4</v>
       </c>
@@ -1207,7 +1244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>3</v>
       </c>
@@ -1215,25 +1252,25 @@
       <c r="C56" s="14"/>
       <c r="D56" s="15">
         <f>SUM(D49:D55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+        <v>537.05000000000007</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B57" s="3"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B58" s="3"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B59" s="3"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>9</v>
       </c>
@@ -1241,12 +1278,12 @@
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
     </row>
-    <row r="61" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="3"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>0</v>
       </c>
@@ -1260,7 +1297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="7"/>
       <c r="B63" s="8"/>
       <c r="C63" s="9"/>
@@ -1269,7 +1306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="7"/>
       <c r="B64" s="8"/>
       <c r="C64" s="9"/>
@@ -1278,7 +1315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="7"/>
       <c r="B65" s="8"/>
       <c r="C65" s="9"/>
@@ -1287,7 +1324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="7"/>
       <c r="B66" s="8"/>
       <c r="C66" s="9"/>
@@ -1296,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="7"/>
       <c r="B67" s="8"/>
       <c r="C67" s="9"/>
@@ -1305,7 +1342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="8"/>
       <c r="C68" s="9"/>
@@ -1314,7 +1351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>4</v>
       </c>
@@ -1325,7 +1362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="12" t="s">
         <v>3</v>
       </c>
